--- a/ForHome8/DataScience/data_audit_task05.xlsx
+++ b/ForHome8/DataScience/data_audit_task05.xlsx
@@ -276,7 +276,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M27"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
@@ -1399,7 +1399,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1442,7 +1442,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1557,7 +1557,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1648,7 +1648,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1707,7 +1707,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1814,7 +1814,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1881,7 +1881,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1964,7 +1964,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2055,7 +2055,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2154,7 +2154,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2213,7 +2213,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2296,7 +2296,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2411,7 +2411,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2502,7 +2502,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2553,7 +2553,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2620,7 +2620,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2727,7 +2727,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2810,7 +2810,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2917,7 +2917,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2984,7 +2984,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3099,7 +3099,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3214,7 +3214,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3313,7 +3313,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3404,7 +3404,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3511,7 +3511,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3594,7 +3594,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
